--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>26529.14</v>
+        <v>26434.69</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20487.68</v>
+        <v>20547.03</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6744.68</v>
+        <v>6764.22</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>48085.11</v>
+        <v>48333.5</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6740.28</v>
+        <v>6775.1</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44990.1</v>
+        <v>45222.5</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>40524.21</v>
+        <v>40733.54</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12586.07</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6112.86</v>
+        <v>6168.46</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23228.27</v>
+        <v>23439.55</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31068.69</v>
+        <v>31285</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6866.66</v>
+        <v>6911.88</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>16458.26</v>
+        <v>16604.85</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8613.200000000001</v>
+        <v>8689.92</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9275.780000000001</v>
+        <v>9259.879999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9839.450000000001</v>
+        <v>9829.309999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>15396.39</v>
+        <v>15286.09</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12721.66</v>
+        <v>12702.95</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>34546.47</v>
+        <v>34495.65</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9310.98</v>
+        <v>9260.280000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6397.29</v>
+        <v>6362.45</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>13838.09</v>
+        <v>13756.54</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13226.18</v>
+        <v>13145.81</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6726.75</v>
+        <v>6685.88</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>39097.12</v>
+        <v>38859.55</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10846.62</v>
+        <v>10780.71</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>15049.75</v>
+        <v>14958.3</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>35519.19</v>
+        <v>35703.08</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>28154.25</v>
+        <v>28181.38</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1570,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1826,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2078,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2265,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3453-51-CM26</t>
+          <t>1208066-75-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -594,37 +594,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20547.03</v>
+        <v>8042.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1456839-6-CM26</t>
+          <t>3453-51-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -669,27 +669,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.981.420-7</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6764.22</v>
+        <v>20547.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1389183-36-CM26</t>
+          <t>1456839-6-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.981.420-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS COPIHUES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -749,28 +749,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>48333.5</v>
+        <v>6764.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5621-56-CM26</t>
+          <t>1389183-36-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -795,47 +799,43 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.100-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>6.189.318-0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6775.1</v>
+        <v>48333.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1475044-20-CM26</t>
+          <t>5621-56-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -875,28 +875,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45222.5</v>
+        <v>6775.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1475044-22-CM26</t>
+          <t>1475044-20-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -936,12 +940,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -951,13 +955,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>40733.54</v>
+        <v>45222.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2446-154-CM26</t>
+          <t>1475044-22-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -972,57 +976,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12533</v>
+        <v>40733.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3453-53-CM26</t>
+          <t>2446-154-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1037,37 +1037,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6168.46</v>
+        <v>12533</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3714-24-CM26</t>
+          <t>3453-53-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1112,43 +1112,47 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23439.55</v>
+        <v>6168.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079713-50-CM26</t>
+          <t>3714-24-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1163,7 +1167,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1173,47 +1177,43 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.322.604-3</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.938-8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31285</v>
+        <v>23439.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>542429-3-CM26</t>
+          <t>1079713-50-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1238,27 +1238,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>53.322.604-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6911.88</v>
+        <v>31285</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2450-122-CM26</t>
+          <t>542429-3-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1303,37 +1303,41 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>16604.85</v>
+        <v>6911.88</v>
       </c>
     </row>
     <row r="15">
@@ -1400,7 +1404,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2467-56-CM26</t>
+          <t>2450-122-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1415,37 +1419,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.208.692-K</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1455,13 +1459,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>9259.879999999999</v>
+        <v>16604.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1475044-26-CM26</t>
+          <t>2467-56-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,37 +1480,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BODEGA STOCK SPA</t>
+          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.744.548-2</t>
+          <t>77.208.692-K</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1516,13 +1520,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9829.309999999999</v>
+        <v>9259.879999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1460278-56-CM26</t>
+          <t>1475044-26-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1537,22 +1541,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1562,32 +1566,28 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>BODEGA STOCK SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.744.548-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>15286.09</v>
+        <v>9829.309999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1233615-74-CM26</t>
+          <t>1460278-56-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1602,53 +1602,57 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>12702.95</v>
+        <v>15286.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1475044-27-CM26</t>
+          <t>1233615-74-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1673,47 +1677,43 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.205.938-8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>34495.65</v>
+        <v>12702.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1082957-46-CM26</t>
+          <t>1475044-27-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.680-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9260.280000000001</v>
+        <v>34495.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3714-33-CM26</t>
+          <t>1082957-46-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>62.000.680-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIRECCION GENERAL DE PROMOCION DE EXPORTACIONES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6362.45</v>
+        <v>9260.280000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057049-11798-CM26</t>
+          <t>3714-33-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1868,27 +1868,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>13756.54</v>
+        <v>6362.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057973-1-CM26</t>
+          <t>1057049-11798-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1948,28 +1948,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13145.81</v>
+        <v>13756.54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1456838-11-CM26</t>
+          <t>1057973-1-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1994,27 +1998,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.981.440-1</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2024,13 +2028,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6685.88</v>
+        <v>13145.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1375757-57-CM26</t>
+          <t>1456838-11-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2055,47 +2059,43 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>38859.55</v>
+        <v>6685.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5684-100-CM26</t>
+          <t>1375757-57-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2135,28 +2135,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>10780.71</v>
+        <v>38859.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4803-61-CM26</t>
+          <t>5684-100-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2176,32 +2180,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2211,13 +2215,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14958.3</v>
+        <v>10780.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1305525-31-CM26</t>
+          <t>4803-61-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2232,22 +2236,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.981.120-8</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2257,86 +2261,147 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.007.474-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>35703.08</v>
+        <v>14958.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>1305525-31-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.981.120-8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>35703.08</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>2378-55-CM26</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>69.070.700-4</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE LA FLORIDA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>JUEGOS MAGICOS</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>76.102.918-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
         <v>28181.38</v>
       </c>
     </row>
